--- a/luban-excels/xlsx/__beans__.xlsx
+++ b/luban-excels/xlsx/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>字段变体</t>
-  </si>
-  <si>
-    <t>CardSkill.Effect</t>
-  </si>
-  <si>
-    <t>技能效果</t>
   </si>
 </sst>
 </file>
@@ -1075,8 +1069,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="37" style="1" customWidth="1"/>
@@ -1197,15 +1191,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" ht="13.8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
